--- a/backend/uploads/individuales/EMERGENCIA/6/Planilla_6_EMERGENCIA.xlsx
+++ b/backend/uploads/individuales/EMERGENCIA/6/Planilla_6_EMERGENCIA.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="52">
   <si>
     <t>CENTRO CLINICO QUIRÚRGICO AMBULATORIO HOSPITAL DEL DÍA CHIMBACALLE</t>
   </si>
@@ -113,28 +113,40 @@
     <t>TOTAL SOLICITADO</t>
   </si>
   <si>
+    <t>3432620053020</t>
+  </si>
+  <si>
+    <t>EQUIPO DE VENOCLISIS CON LLAVE DE TRES VIAS</t>
+  </si>
+  <si>
+    <t>EM09-38</t>
+  </si>
+  <si>
+    <t>397153</t>
+  </si>
+  <si>
+    <t>Punto de arranque</t>
+  </si>
+  <si>
+    <t>EM21-65</t>
+  </si>
+  <si>
+    <t>397164</t>
+  </si>
+  <si>
+    <t>Ambulancia pago por Km recorrido ida y vuelta,  más de 20 km.</t>
+  </si>
+  <si>
     <t>3432620068050</t>
   </si>
   <si>
     <t>GUANTES DE LATEX, TALLA PEQUEÑO</t>
   </si>
   <si>
-    <t>EM09-38</t>
-  </si>
-  <si>
-    <t>397153</t>
-  </si>
-  <si>
-    <t>Punto de arranque</t>
-  </si>
-  <si>
-    <t>EM21-65</t>
-  </si>
-  <si>
-    <t>3432620053020</t>
-  </si>
-  <si>
-    <t>EQUIPO DE VENOCLISIS CON LLAVE DE TRES VIAS</t>
+    <t>3432620036090</t>
+  </si>
+  <si>
+    <t>CATETER INTRAVENOSO 22 G CON ALETAS</t>
   </si>
   <si>
     <t>3213305026</t>
@@ -146,22 +158,10 @@
     <t>EM12-45</t>
   </si>
   <si>
-    <t>397164</t>
-  </si>
-  <si>
-    <t>Ambulancia pago por Km recorrido ida y vuelta,  más de 20 km.</t>
-  </si>
-  <si>
-    <t>3432620036090</t>
-  </si>
-  <si>
-    <t>CATETER INTRAVENOSO 22 G CON ALETAS</t>
-  </si>
-  <si>
     <t>TOTAL VALOR SOLICITADO</t>
   </si>
   <si>
-    <t>Treinta Dólares 08/100</t>
+    <t>Treinta y dos Dólares 21/100</t>
   </si>
   <si>
     <t>NOMBRE:</t>
@@ -173,19 +173,13 @@
     <t>DOCUMENTO DE IDENTIDAD:</t>
   </si>
   <si>
-    <t>1234567890</t>
-  </si>
-  <si>
     <t xml:space="preserve">CARGO: </t>
   </si>
   <si>
-    <t>ANALISTA - FACTURACIÓN</t>
+    <t>RESPONSABLE DE FACTURACION</t>
   </si>
   <si>
     <t>Econ. Ximena Cobos</t>
-  </si>
-  <si>
-    <t>1324567890</t>
   </si>
   <si>
     <t>DIRECTOR ADMINISTRATIVO</t>
@@ -1213,7 +1207,7 @@
       <c r="E6" s="19"/>
       <c r="F6" s="19"/>
       <c r="G6" s="20">
-        <v>46235</v>
+        <v>46266</v>
       </c>
       <c r="H6" s="21"/>
       <c r="I6" s="22"/>
@@ -1224,7 +1218,7 @@
       </c>
       <c r="B7" s="18"/>
       <c r="C7" s="23">
-        <v>30.080000000000002</v>
+        <v>32.21</v>
       </c>
       <c r="D7" s="18" t="s">
         <v>8</v>
@@ -1290,13 +1284,13 @@
         <v>17</v>
       </c>
       <c r="C11" s="31">
-        <v>45887</v>
+        <v>46009</v>
       </c>
       <c r="D11" s="30" t="s">
         <v>18</v>
       </c>
       <c r="E11" s="31">
-        <v>45887</v>
+        <v>46009</v>
       </c>
       <c r="F11" s="30"/>
       <c r="G11" s="30"/>
@@ -1334,7 +1328,7 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="36">
-        <v>45887</v>
+        <v>46009</v>
       </c>
       <c r="B13" s="36" t="s">
         <v>28</v>
@@ -1343,13 +1337,13 @@
         <v>29</v>
       </c>
       <c r="D13" s="36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E13" s="36">
-        <v>0.07</v>
+        <v>1.53</v>
       </c>
       <c r="F13" s="36">
-        <v>0.14</v>
+        <v>1.53</v>
       </c>
       <c r="G13" s="36" t="s">
         <v>30</v>
@@ -1358,12 +1352,12 @@
         <v>100</v>
       </c>
       <c r="I13" s="36">
-        <v>0.14</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="14" ht="37.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="36">
-        <v>45887</v>
+        <v>46009</v>
       </c>
       <c r="B14" s="36" t="s">
         <v>31</v>
@@ -1392,7 +1386,7 @@
     </row>
     <row r="15" ht="39" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="36">
-        <v>45887</v>
+        <v>46009</v>
       </c>
       <c r="B15" s="36" t="s">
         <v>34</v>
@@ -1401,27 +1395,27 @@
         <v>35</v>
       </c>
       <c r="D15" s="36">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E15" s="36">
-        <v>1.53</v>
+        <v>1.34</v>
       </c>
       <c r="F15" s="36">
-        <v>1.53</v>
+        <v>5.36</v>
       </c>
       <c r="G15" s="36" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H15" s="36">
         <v>100</v>
       </c>
       <c r="I15" s="36">
-        <v>1.53</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="36">
-        <v>45887</v>
+        <v>46009</v>
       </c>
       <c r="B16" s="36" t="s">
         <v>36</v>
@@ -1430,80 +1424,80 @@
         <v>37</v>
       </c>
       <c r="D16" s="36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="36">
-        <v>0.69</v>
+        <v>0.07</v>
       </c>
       <c r="F16" s="36">
-        <v>0.69</v>
+        <v>0.14</v>
       </c>
       <c r="G16" s="36" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="H16" s="36">
         <v>100</v>
       </c>
       <c r="I16" s="36">
-        <v>0.69</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="36">
-        <v>45887</v>
+        <v>46009</v>
       </c>
       <c r="B17" s="36" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" s="36" t="s">
         <v>39</v>
       </c>
-      <c r="C17" s="36" t="s">
-        <v>40</v>
-      </c>
       <c r="D17" s="36">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E17" s="36">
-        <v>1.34</v>
+        <v>1.79</v>
       </c>
       <c r="F17" s="36">
-        <v>5.36</v>
+        <v>1.79</v>
       </c>
       <c r="G17" s="36" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H17" s="36">
         <v>100</v>
       </c>
       <c r="I17" s="36">
-        <v>5.36</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="36">
-        <v>45887</v>
+        <v>46009</v>
       </c>
       <c r="B18" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="36" t="s">
         <v>41</v>
-      </c>
-      <c r="C18" s="36" t="s">
-        <v>42</v>
       </c>
       <c r="D18" s="36">
         <v>1</v>
       </c>
       <c r="E18" s="36">
-        <v>1.79</v>
+        <v>0.69</v>
       </c>
       <c r="F18" s="36">
-        <v>1.79</v>
+        <v>0.69</v>
       </c>
       <c r="G18" s="36" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="H18" s="36">
         <v>100</v>
       </c>
       <c r="I18" s="36">
-        <v>1.79</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
@@ -1905,7 +1899,7 @@
       <c r="G54" s="41"/>
       <c r="H54" s="42"/>
       <c r="I54" s="43">
-        <v>30.080000000000002</v>
+        <v>32.21</v>
       </c>
     </row>
     <row r="55" ht="90.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1984,7 +1978,7 @@
         <v>47</v>
       </c>
       <c r="C61" s="56" t="s">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="D61" s="53"/>
       <c r="E61" s="53"/>
@@ -1996,10 +1990,10 @@
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="47"/>
       <c r="B62" s="57" t="s">
+        <v>48</v>
+      </c>
+      <c r="C62" s="58" t="s">
         <v>49</v>
-      </c>
-      <c r="C62" s="58" t="s">
-        <v>50</v>
       </c>
       <c r="D62" s="53"/>
       <c r="E62" s="53"/>
@@ -2036,7 +2030,7 @@
         <v>45</v>
       </c>
       <c r="C65" s="51" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D65" s="53"/>
       <c r="E65" s="53"/>
@@ -2051,7 +2045,7 @@
         <v>47</v>
       </c>
       <c r="C66" s="56" t="s">
-        <v>52</v>
+        <v>11</v>
       </c>
       <c r="D66" s="53"/>
       <c r="E66" s="53"/>
@@ -2063,10 +2057,10 @@
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="47"/>
       <c r="B67" s="57" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C67" s="58" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D67" s="53"/>
       <c r="E67" s="53"/>

--- a/backend/uploads/individuales/EMERGENCIA/6/Planilla_6_EMERGENCIA.xlsx
+++ b/backend/uploads/individuales/EMERGENCIA/6/Planilla_6_EMERGENCIA.xlsx
@@ -12,14 +12,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase">'FORMATO PLANILLA INDIVIDUAL'!$J$12:$O$13</definedName>
-    <definedName name="CIE">'[2]cie10'!$A$1:$A$14418</definedName>
-    <definedName name="clinica">'[2]modificadores'!$A$6:$C$11</definedName>
-    <definedName name="modificador">'[2]modificadores'!$A$2:$A$35</definedName>
-    <definedName name="modificadoresvalor">'[2]modificadores'!$A$2:$B$35</definedName>
-    <definedName name="obscontroltarifas">'[2]causasdebito'!$A$5:$A$14</definedName>
-    <definedName name="obsmedico">'[2]causasdebito'!$A$16:$A$91</definedName>
-    <definedName name="TNS">'[2]tns'!$A$1:$B$9168</definedName>
-    <definedName name="TNSVALORES">'[2]tns'!$A$1:$C$9168</definedName>
+    <definedName name="CIE">'[1]cie10'!$A$1:$A$14418</definedName>
+    <definedName name="clinica">'[1]modificadores'!$A$6:$C$11</definedName>
+    <definedName name="modificador">'[1]modificadores'!$A$2:$A$35</definedName>
+    <definedName name="modificadoresvalor">'[1]modificadores'!$A$2:$B$35</definedName>
+    <definedName name="obscontroltarifas">'[1]causasdebito'!$A$5:$A$14</definedName>
+    <definedName name="obsmedico">'[1]causasdebito'!$A$16:$A$91</definedName>
+    <definedName name="TNS">'[1]tns'!$A$1:$B$9168</definedName>
+    <definedName name="TNSVALORES">'[1]tns'!$A$1:$C$9168</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'FORMATO PLANILLA INDIVIDUAL'!$A1:$I68</definedName>
   </definedNames>
   <calcPr calcId="171027"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="54">
   <si>
     <t>CENTRO CLINICO QUIRÚRGICO AMBULATORIO HOSPITAL DEL DÍA CHIMBACALLE</t>
   </si>
@@ -113,6 +113,15 @@
     <t>TOTAL SOLICITADO</t>
   </si>
   <si>
+    <t>3213305026</t>
+  </si>
+  <si>
+    <t>CLORURO DE SODIO LQ.PAR. 0,9% FUN/BOL X 500 ML FLX-AUTCP C/SF SELL.HERMT.</t>
+  </si>
+  <si>
+    <t>EM12-45</t>
+  </si>
+  <si>
     <t>3432620053020</t>
   </si>
   <si>
@@ -122,6 +131,18 @@
     <t>EM09-38</t>
   </si>
   <si>
+    <t>3432620036090</t>
+  </si>
+  <si>
+    <t>CATETER INTRAVENOSO 22 G CON ALETAS</t>
+  </si>
+  <si>
+    <t>3432620068050</t>
+  </si>
+  <si>
+    <t>GUANTES DE LATEX, TALLA PEQUEÑO</t>
+  </si>
+  <si>
     <t>397153</t>
   </si>
   <si>
@@ -137,31 +158,10 @@
     <t>Ambulancia pago por Km recorrido ida y vuelta,  más de 20 km.</t>
   </si>
   <si>
-    <t>3432620068050</t>
-  </si>
-  <si>
-    <t>GUANTES DE LATEX, TALLA PEQUEÑO</t>
-  </si>
-  <si>
-    <t>3432620036090</t>
-  </si>
-  <si>
-    <t>CATETER INTRAVENOSO 22 G CON ALETAS</t>
-  </si>
-  <si>
-    <t>3213305026</t>
-  </si>
-  <si>
-    <t>CLORURO DE SODIO LQ.PAR. 0,9% FUN/BOL X 500 ML FLX-AUTCP C/SF SELL.HERMT.</t>
-  </si>
-  <si>
-    <t>EM12-45</t>
-  </si>
-  <si>
     <t>TOTAL VALOR SOLICITADO</t>
   </si>
   <si>
-    <t>Treinta y dos Dólares 21/100</t>
+    <t>Treinta Dólares 08/100</t>
   </si>
   <si>
     <t>NOMBRE:</t>
@@ -173,13 +173,19 @@
     <t>DOCUMENTO DE IDENTIDAD:</t>
   </si>
   <si>
+    <t>1234567890</t>
+  </si>
+  <si>
     <t xml:space="preserve">CARGO: </t>
   </si>
   <si>
-    <t>RESPONSABLE DE FACTURACION</t>
+    <t>ANALISTA - FACTURACION</t>
   </si>
   <si>
     <t>Econ. Ximena Cobos</t>
+  </si>
+  <si>
+    <t>1324567890</t>
   </si>
   <si>
     <t>DIRECTOR ADMINISTRATIVO</t>
@@ -189,11 +195,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="4">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="mmmm/yyyy"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="166" formatCode="0000000000"/>
-    <numFmt numFmtId="167" formatCode="_ * #,##0.00_ ;_ * -#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="167" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="168" formatCode="0.##"/>
+    <numFmt numFmtId="169" formatCode="0.0000"/>
+    <numFmt numFmtId="170" formatCode="0.00&quot;%&quot;"/>
+    <numFmt numFmtId="171" formatCode="_ * #,##0.00_ ;_ * -#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -529,7 +539,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection locked="0"/>
@@ -644,7 +654,7 @@
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="6" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="167" fontId="6" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
@@ -664,10 +674,30 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="169" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="170" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -692,7 +722,7 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="171" fontId="3" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1218,7 +1248,7 @@
       </c>
       <c r="B7" s="18"/>
       <c r="C7" s="23">
-        <v>32.21</v>
+        <v>30.08</v>
       </c>
       <c r="D7" s="18" t="s">
         <v>8</v>
@@ -1330,755 +1360,755 @@
       <c r="A13" s="36">
         <v>46009</v>
       </c>
-      <c r="B13" s="36" t="s">
+      <c r="B13" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="36" t="s">
+      <c r="C13" s="37" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="36">
+      <c r="D13" s="38">
         <v>1</v>
       </c>
-      <c r="E13" s="36">
-        <v>1.53</v>
-      </c>
-      <c r="F13" s="36">
-        <v>1.53</v>
-      </c>
-      <c r="G13" s="36" t="s">
+      <c r="E13" s="39">
+        <v>0.69</v>
+      </c>
+      <c r="F13" s="40">
+        <v>0.69</v>
+      </c>
+      <c r="G13" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="H13" s="36">
+      <c r="H13" s="41">
         <v>100</v>
       </c>
-      <c r="I13" s="36">
-        <v>1.57</v>
+      <c r="I13" s="40">
+        <v>0.69</v>
       </c>
     </row>
     <row r="14" ht="37.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="36">
         <v>46009</v>
       </c>
-      <c r="B14" s="36" t="s">
+      <c r="B14" s="37" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="36" t="s">
+      <c r="C14" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="D14" s="36">
+      <c r="D14" s="38">
         <v>1</v>
       </c>
-      <c r="E14" s="36">
-        <v>20.57</v>
-      </c>
-      <c r="F14" s="36">
-        <v>20.57</v>
-      </c>
-      <c r="G14" s="36" t="s">
+      <c r="E14" s="39">
+        <v>1.53</v>
+      </c>
+      <c r="F14" s="40">
+        <v>1.53</v>
+      </c>
+      <c r="G14" s="37" t="s">
         <v>33</v>
       </c>
-      <c r="H14" s="36">
+      <c r="H14" s="41">
         <v>100</v>
       </c>
-      <c r="I14" s="36">
-        <v>20.57</v>
+      <c r="I14" s="40">
+        <v>1.53</v>
       </c>
     </row>
     <row r="15" ht="39" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="36">
         <v>46009</v>
       </c>
-      <c r="B15" s="36" t="s">
+      <c r="B15" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="C15" s="36" t="s">
+      <c r="C15" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="D15" s="36">
-        <v>4</v>
-      </c>
-      <c r="E15" s="36">
-        <v>1.34</v>
-      </c>
-      <c r="F15" s="36">
-        <v>5.36</v>
-      </c>
-      <c r="G15" s="36" t="s">
+      <c r="D15" s="38">
+        <v>1</v>
+      </c>
+      <c r="E15" s="39">
+        <v>1.79</v>
+      </c>
+      <c r="F15" s="40">
+        <v>1.79</v>
+      </c>
+      <c r="G15" s="37" t="s">
         <v>33</v>
       </c>
-      <c r="H15" s="36">
+      <c r="H15" s="41">
         <v>100</v>
       </c>
-      <c r="I15" s="36">
-        <v>5.36</v>
+      <c r="I15" s="40">
+        <v>1.79</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="36">
         <v>46009</v>
       </c>
-      <c r="B16" s="36" t="s">
+      <c r="B16" s="37" t="s">
         <v>36</v>
       </c>
-      <c r="C16" s="36" t="s">
+      <c r="C16" s="37" t="s">
         <v>37</v>
       </c>
-      <c r="D16" s="36">
+      <c r="D16" s="38">
         <v>2</v>
       </c>
-      <c r="E16" s="36">
+      <c r="E16" s="39">
         <v>0.07</v>
       </c>
-      <c r="F16" s="36">
+      <c r="F16" s="40">
         <v>0.14</v>
       </c>
-      <c r="G16" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="H16" s="36">
+      <c r="G16" s="37" t="s">
+        <v>33</v>
+      </c>
+      <c r="H16" s="41">
         <v>100</v>
       </c>
-      <c r="I16" s="36">
-        <v>1.57</v>
+      <c r="I16" s="40">
+        <v>0.14</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="36">
         <v>46009</v>
       </c>
-      <c r="B17" s="36" t="s">
+      <c r="B17" s="37" t="s">
         <v>38</v>
       </c>
-      <c r="C17" s="36" t="s">
+      <c r="C17" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="D17" s="36">
+      <c r="D17" s="38">
         <v>1</v>
       </c>
-      <c r="E17" s="36">
-        <v>1.79</v>
-      </c>
-      <c r="F17" s="36">
-        <v>1.79</v>
-      </c>
-      <c r="G17" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="H17" s="36">
+      <c r="E17" s="39">
+        <v>20.57</v>
+      </c>
+      <c r="F17" s="40">
+        <v>20.57</v>
+      </c>
+      <c r="G17" s="37" t="s">
+        <v>40</v>
+      </c>
+      <c r="H17" s="41">
         <v>100</v>
       </c>
-      <c r="I17" s="36">
-        <v>1.57</v>
+      <c r="I17" s="40">
+        <v>20.57</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="36">
         <v>46009</v>
       </c>
-      <c r="B18" s="36" t="s">
+      <c r="B18" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="C18" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="D18" s="38">
+        <v>4</v>
+      </c>
+      <c r="E18" s="39">
+        <v>1.34</v>
+      </c>
+      <c r="F18" s="40">
+        <v>5.36</v>
+      </c>
+      <c r="G18" s="37" t="s">
         <v>40</v>
       </c>
-      <c r="C18" s="36" t="s">
-        <v>41</v>
-      </c>
-      <c r="D18" s="36">
-        <v>1</v>
-      </c>
-      <c r="E18" s="36">
-        <v>0.69</v>
-      </c>
-      <c r="F18" s="36">
-        <v>0.69</v>
-      </c>
-      <c r="G18" s="36" t="s">
-        <v>42</v>
-      </c>
-      <c r="H18" s="36">
+      <c r="H18" s="41">
         <v>100</v>
       </c>
-      <c r="I18" s="36">
-        <v>1.57</v>
+      <c r="I18" s="40">
+        <v>5.36</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="36"/>
-      <c r="B19" s="36"/>
-      <c r="C19" s="36"/>
-      <c r="D19" s="36"/>
-      <c r="E19" s="36"/>
-      <c r="F19" s="36"/>
-      <c r="G19" s="36"/>
-      <c r="H19" s="36"/>
-      <c r="I19" s="36"/>
+      <c r="A19" s="37"/>
+      <c r="B19" s="37"/>
+      <c r="C19" s="37"/>
+      <c r="D19" s="37"/>
+      <c r="E19" s="37"/>
+      <c r="F19" s="37"/>
+      <c r="G19" s="37"/>
+      <c r="H19" s="37"/>
+      <c r="I19" s="37"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="36"/>
-      <c r="B20" s="36"/>
-      <c r="C20" s="36"/>
-      <c r="D20" s="36"/>
-      <c r="E20" s="36"/>
-      <c r="F20" s="36"/>
-      <c r="G20" s="36"/>
-      <c r="H20" s="36"/>
-      <c r="I20" s="36"/>
+      <c r="A20" s="37"/>
+      <c r="B20" s="37"/>
+      <c r="C20" s="37"/>
+      <c r="D20" s="37"/>
+      <c r="E20" s="37"/>
+      <c r="F20" s="37"/>
+      <c r="G20" s="37"/>
+      <c r="H20" s="37"/>
+      <c r="I20" s="37"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="36"/>
-      <c r="B21" s="36"/>
-      <c r="C21" s="36"/>
-      <c r="D21" s="36"/>
-      <c r="E21" s="36"/>
-      <c r="F21" s="36"/>
-      <c r="G21" s="36"/>
-      <c r="H21" s="36"/>
-      <c r="I21" s="36"/>
+      <c r="A21" s="37"/>
+      <c r="B21" s="37"/>
+      <c r="C21" s="37"/>
+      <c r="D21" s="37"/>
+      <c r="E21" s="37"/>
+      <c r="F21" s="37"/>
+      <c r="G21" s="37"/>
+      <c r="H21" s="37"/>
+      <c r="I21" s="37"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="36"/>
-      <c r="B22" s="36"/>
-      <c r="C22" s="36"/>
-      <c r="D22" s="36"/>
-      <c r="E22" s="36"/>
-      <c r="F22" s="36"/>
-      <c r="G22" s="36"/>
-      <c r="H22" s="36"/>
-      <c r="I22" s="36"/>
+      <c r="A22" s="37"/>
+      <c r="B22" s="37"/>
+      <c r="C22" s="37"/>
+      <c r="D22" s="37"/>
+      <c r="E22" s="37"/>
+      <c r="F22" s="37"/>
+      <c r="G22" s="37"/>
+      <c r="H22" s="37"/>
+      <c r="I22" s="37"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="36"/>
-      <c r="B23" s="36"/>
-      <c r="C23" s="36"/>
-      <c r="D23" s="36"/>
-      <c r="E23" s="36"/>
-      <c r="F23" s="36"/>
-      <c r="G23" s="36"/>
-      <c r="H23" s="36"/>
-      <c r="I23" s="36"/>
+      <c r="A23" s="37"/>
+      <c r="B23" s="37"/>
+      <c r="C23" s="37"/>
+      <c r="D23" s="37"/>
+      <c r="E23" s="37"/>
+      <c r="F23" s="37"/>
+      <c r="G23" s="37"/>
+      <c r="H23" s="37"/>
+      <c r="I23" s="37"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="36"/>
-      <c r="B24" s="36"/>
-      <c r="C24" s="36"/>
-      <c r="D24" s="36"/>
-      <c r="E24" s="36"/>
-      <c r="F24" s="36"/>
-      <c r="G24" s="36"/>
-      <c r="H24" s="36"/>
-      <c r="I24" s="36"/>
+      <c r="A24" s="37"/>
+      <c r="B24" s="37"/>
+      <c r="C24" s="37"/>
+      <c r="D24" s="37"/>
+      <c r="E24" s="37"/>
+      <c r="F24" s="37"/>
+      <c r="G24" s="37"/>
+      <c r="H24" s="37"/>
+      <c r="I24" s="37"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="36"/>
-      <c r="B25" s="36"/>
-      <c r="C25" s="36"/>
-      <c r="D25" s="36"/>
-      <c r="E25" s="36"/>
-      <c r="F25" s="36"/>
-      <c r="G25" s="36"/>
-      <c r="H25" s="36"/>
-      <c r="I25" s="36"/>
+      <c r="A25" s="37"/>
+      <c r="B25" s="37"/>
+      <c r="C25" s="37"/>
+      <c r="D25" s="37"/>
+      <c r="E25" s="37"/>
+      <c r="F25" s="37"/>
+      <c r="G25" s="37"/>
+      <c r="H25" s="37"/>
+      <c r="I25" s="37"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="36"/>
-      <c r="B26" s="36"/>
-      <c r="C26" s="36"/>
-      <c r="D26" s="36"/>
-      <c r="E26" s="36"/>
-      <c r="F26" s="36"/>
-      <c r="G26" s="36"/>
-      <c r="H26" s="36"/>
-      <c r="I26" s="36"/>
+      <c r="A26" s="37"/>
+      <c r="B26" s="37"/>
+      <c r="C26" s="37"/>
+      <c r="D26" s="37"/>
+      <c r="E26" s="37"/>
+      <c r="F26" s="37"/>
+      <c r="G26" s="37"/>
+      <c r="H26" s="37"/>
+      <c r="I26" s="37"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="36"/>
-      <c r="B27" s="36"/>
-      <c r="C27" s="36"/>
-      <c r="D27" s="36"/>
-      <c r="E27" s="36"/>
-      <c r="F27" s="36"/>
-      <c r="G27" s="36"/>
-      <c r="H27" s="36"/>
-      <c r="I27" s="36"/>
+      <c r="A27" s="37"/>
+      <c r="B27" s="37"/>
+      <c r="C27" s="37"/>
+      <c r="D27" s="37"/>
+      <c r="E27" s="37"/>
+      <c r="F27" s="37"/>
+      <c r="G27" s="37"/>
+      <c r="H27" s="37"/>
+      <c r="I27" s="37"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="36"/>
-      <c r="B28" s="36"/>
-      <c r="C28" s="36"/>
-      <c r="D28" s="36"/>
-      <c r="E28" s="36"/>
-      <c r="F28" s="36"/>
-      <c r="G28" s="36"/>
-      <c r="H28" s="36"/>
-      <c r="I28" s="36"/>
+      <c r="A28" s="37"/>
+      <c r="B28" s="37"/>
+      <c r="C28" s="37"/>
+      <c r="D28" s="37"/>
+      <c r="E28" s="37"/>
+      <c r="F28" s="37"/>
+      <c r="G28" s="37"/>
+      <c r="H28" s="37"/>
+      <c r="I28" s="37"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="36"/>
-      <c r="B29" s="36"/>
-      <c r="C29" s="36"/>
-      <c r="D29" s="36"/>
-      <c r="E29" s="36"/>
-      <c r="F29" s="36"/>
-      <c r="G29" s="36"/>
-      <c r="H29" s="36"/>
-      <c r="I29" s="36"/>
+      <c r="A29" s="37"/>
+      <c r="B29" s="37"/>
+      <c r="C29" s="37"/>
+      <c r="D29" s="37"/>
+      <c r="E29" s="37"/>
+      <c r="F29" s="37"/>
+      <c r="G29" s="37"/>
+      <c r="H29" s="37"/>
+      <c r="I29" s="37"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="36"/>
-      <c r="B30" s="36"/>
-      <c r="C30" s="36"/>
-      <c r="D30" s="36"/>
-      <c r="E30" s="36"/>
-      <c r="F30" s="36"/>
-      <c r="G30" s="36"/>
-      <c r="H30" s="36"/>
-      <c r="I30" s="36"/>
+      <c r="A30" s="37"/>
+      <c r="B30" s="37"/>
+      <c r="C30" s="37"/>
+      <c r="D30" s="37"/>
+      <c r="E30" s="37"/>
+      <c r="F30" s="37"/>
+      <c r="G30" s="37"/>
+      <c r="H30" s="37"/>
+      <c r="I30" s="37"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="36"/>
-      <c r="B31" s="36"/>
-      <c r="C31" s="36"/>
-      <c r="D31" s="36"/>
-      <c r="E31" s="36"/>
-      <c r="F31" s="36"/>
-      <c r="G31" s="36"/>
-      <c r="H31" s="36"/>
-      <c r="I31" s="36"/>
+      <c r="A31" s="37"/>
+      <c r="B31" s="37"/>
+      <c r="C31" s="37"/>
+      <c r="D31" s="37"/>
+      <c r="E31" s="37"/>
+      <c r="F31" s="37"/>
+      <c r="G31" s="37"/>
+      <c r="H31" s="37"/>
+      <c r="I31" s="37"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="36"/>
-      <c r="B32" s="36"/>
-      <c r="C32" s="36"/>
-      <c r="D32" s="36"/>
-      <c r="E32" s="36"/>
-      <c r="F32" s="36"/>
-      <c r="G32" s="36"/>
-      <c r="H32" s="36"/>
-      <c r="I32" s="36"/>
+      <c r="A32" s="37"/>
+      <c r="B32" s="37"/>
+      <c r="C32" s="37"/>
+      <c r="D32" s="37"/>
+      <c r="E32" s="37"/>
+      <c r="F32" s="37"/>
+      <c r="G32" s="37"/>
+      <c r="H32" s="37"/>
+      <c r="I32" s="37"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" s="36"/>
-      <c r="B33" s="36"/>
-      <c r="C33" s="36"/>
-      <c r="D33" s="36"/>
-      <c r="E33" s="36"/>
-      <c r="F33" s="36"/>
-      <c r="G33" s="36"/>
-      <c r="H33" s="36"/>
-      <c r="I33" s="36"/>
+      <c r="A33" s="37"/>
+      <c r="B33" s="37"/>
+      <c r="C33" s="37"/>
+      <c r="D33" s="37"/>
+      <c r="E33" s="37"/>
+      <c r="F33" s="37"/>
+      <c r="G33" s="37"/>
+      <c r="H33" s="37"/>
+      <c r="I33" s="37"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="36"/>
-      <c r="B34" s="36"/>
-      <c r="C34" s="36"/>
-      <c r="D34" s="36"/>
-      <c r="E34" s="36"/>
-      <c r="F34" s="36"/>
-      <c r="G34" s="36"/>
-      <c r="H34" s="36"/>
-      <c r="I34" s="36"/>
+      <c r="A34" s="37"/>
+      <c r="B34" s="37"/>
+      <c r="C34" s="37"/>
+      <c r="D34" s="37"/>
+      <c r="E34" s="37"/>
+      <c r="F34" s="37"/>
+      <c r="G34" s="37"/>
+      <c r="H34" s="37"/>
+      <c r="I34" s="37"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="36"/>
-      <c r="B35" s="36"/>
-      <c r="C35" s="36"/>
-      <c r="D35" s="36"/>
-      <c r="E35" s="36"/>
-      <c r="F35" s="36"/>
-      <c r="G35" s="36"/>
-      <c r="H35" s="36"/>
-      <c r="I35" s="36"/>
+      <c r="A35" s="37"/>
+      <c r="B35" s="37"/>
+      <c r="C35" s="37"/>
+      <c r="D35" s="37"/>
+      <c r="E35" s="37"/>
+      <c r="F35" s="37"/>
+      <c r="G35" s="37"/>
+      <c r="H35" s="37"/>
+      <c r="I35" s="37"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" s="36"/>
-      <c r="B36" s="36"/>
-      <c r="C36" s="36"/>
-      <c r="D36" s="36"/>
-      <c r="E36" s="36"/>
-      <c r="F36" s="36"/>
-      <c r="G36" s="36"/>
-      <c r="H36" s="36"/>
-      <c r="I36" s="36"/>
+      <c r="A36" s="37"/>
+      <c r="B36" s="37"/>
+      <c r="C36" s="37"/>
+      <c r="D36" s="37"/>
+      <c r="E36" s="37"/>
+      <c r="F36" s="37"/>
+      <c r="G36" s="37"/>
+      <c r="H36" s="37"/>
+      <c r="I36" s="37"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" s="36"/>
-      <c r="B37" s="36"/>
-      <c r="C37" s="36"/>
-      <c r="D37" s="36"/>
-      <c r="E37" s="36"/>
-      <c r="F37" s="36"/>
-      <c r="G37" s="36"/>
-      <c r="H37" s="36"/>
-      <c r="I37" s="36"/>
+      <c r="A37" s="37"/>
+      <c r="B37" s="37"/>
+      <c r="C37" s="37"/>
+      <c r="D37" s="37"/>
+      <c r="E37" s="37"/>
+      <c r="F37" s="37"/>
+      <c r="G37" s="37"/>
+      <c r="H37" s="37"/>
+      <c r="I37" s="37"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38" s="36"/>
-      <c r="B38" s="36"/>
-      <c r="C38" s="36"/>
-      <c r="D38" s="36"/>
-      <c r="E38" s="36"/>
-      <c r="F38" s="36"/>
-      <c r="G38" s="36"/>
-      <c r="H38" s="36"/>
-      <c r="I38" s="36"/>
+      <c r="A38" s="37"/>
+      <c r="B38" s="37"/>
+      <c r="C38" s="37"/>
+      <c r="D38" s="37"/>
+      <c r="E38" s="37"/>
+      <c r="F38" s="37"/>
+      <c r="G38" s="37"/>
+      <c r="H38" s="37"/>
+      <c r="I38" s="37"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A39" s="36"/>
-      <c r="B39" s="36"/>
-      <c r="C39" s="36"/>
-      <c r="D39" s="36"/>
-      <c r="E39" s="36"/>
-      <c r="F39" s="36"/>
-      <c r="G39" s="36"/>
-      <c r="H39" s="36"/>
-      <c r="I39" s="36"/>
+      <c r="A39" s="37"/>
+      <c r="B39" s="37"/>
+      <c r="C39" s="37"/>
+      <c r="D39" s="37"/>
+      <c r="E39" s="37"/>
+      <c r="F39" s="37"/>
+      <c r="G39" s="37"/>
+      <c r="H39" s="37"/>
+      <c r="I39" s="37"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A40" s="36"/>
-      <c r="B40" s="36"/>
-      <c r="C40" s="36"/>
-      <c r="D40" s="36"/>
-      <c r="E40" s="36"/>
-      <c r="F40" s="36"/>
-      <c r="G40" s="36"/>
-      <c r="H40" s="36"/>
-      <c r="I40" s="36"/>
+      <c r="A40" s="37"/>
+      <c r="B40" s="37"/>
+      <c r="C40" s="37"/>
+      <c r="D40" s="37"/>
+      <c r="E40" s="37"/>
+      <c r="F40" s="37"/>
+      <c r="G40" s="37"/>
+      <c r="H40" s="37"/>
+      <c r="I40" s="37"/>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" s="36"/>
-      <c r="B41" s="36"/>
-      <c r="C41" s="36"/>
-      <c r="D41" s="36"/>
-      <c r="E41" s="36"/>
-      <c r="F41" s="36"/>
-      <c r="G41" s="36"/>
-      <c r="H41" s="36"/>
-      <c r="I41" s="36"/>
+      <c r="A41" s="37"/>
+      <c r="B41" s="37"/>
+      <c r="C41" s="37"/>
+      <c r="D41" s="37"/>
+      <c r="E41" s="37"/>
+      <c r="F41" s="37"/>
+      <c r="G41" s="37"/>
+      <c r="H41" s="37"/>
+      <c r="I41" s="37"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A42" s="36"/>
-      <c r="B42" s="36"/>
-      <c r="C42" s="36"/>
-      <c r="D42" s="36"/>
-      <c r="E42" s="36"/>
-      <c r="F42" s="36"/>
-      <c r="G42" s="36"/>
-      <c r="H42" s="36"/>
-      <c r="I42" s="36"/>
+      <c r="A42" s="37"/>
+      <c r="B42" s="37"/>
+      <c r="C42" s="37"/>
+      <c r="D42" s="37"/>
+      <c r="E42" s="37"/>
+      <c r="F42" s="37"/>
+      <c r="G42" s="37"/>
+      <c r="H42" s="37"/>
+      <c r="I42" s="37"/>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A43" s="36"/>
-      <c r="B43" s="36"/>
-      <c r="C43" s="36"/>
-      <c r="D43" s="36"/>
-      <c r="E43" s="36"/>
-      <c r="F43" s="36"/>
-      <c r="G43" s="36"/>
-      <c r="H43" s="36"/>
-      <c r="I43" s="36"/>
+      <c r="A43" s="37"/>
+      <c r="B43" s="37"/>
+      <c r="C43" s="37"/>
+      <c r="D43" s="37"/>
+      <c r="E43" s="37"/>
+      <c r="F43" s="37"/>
+      <c r="G43" s="37"/>
+      <c r="H43" s="37"/>
+      <c r="I43" s="37"/>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A44" s="36"/>
-      <c r="B44" s="36"/>
-      <c r="C44" s="36"/>
-      <c r="D44" s="36"/>
-      <c r="E44" s="36"/>
-      <c r="F44" s="36"/>
-      <c r="G44" s="36"/>
-      <c r="H44" s="36"/>
-      <c r="I44" s="36"/>
+      <c r="A44" s="37"/>
+      <c r="B44" s="37"/>
+      <c r="C44" s="37"/>
+      <c r="D44" s="37"/>
+      <c r="E44" s="37"/>
+      <c r="F44" s="37"/>
+      <c r="G44" s="37"/>
+      <c r="H44" s="37"/>
+      <c r="I44" s="37"/>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A45" s="36"/>
-      <c r="B45" s="36"/>
-      <c r="C45" s="36"/>
-      <c r="D45" s="36"/>
-      <c r="E45" s="36"/>
-      <c r="F45" s="36"/>
-      <c r="G45" s="36"/>
-      <c r="H45" s="36"/>
-      <c r="I45" s="36"/>
+      <c r="A45" s="37"/>
+      <c r="B45" s="37"/>
+      <c r="C45" s="37"/>
+      <c r="D45" s="37"/>
+      <c r="E45" s="37"/>
+      <c r="F45" s="37"/>
+      <c r="G45" s="37"/>
+      <c r="H45" s="37"/>
+      <c r="I45" s="37"/>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A46" s="36"/>
-      <c r="B46" s="36"/>
-      <c r="C46" s="36"/>
-      <c r="D46" s="36"/>
-      <c r="E46" s="36"/>
-      <c r="F46" s="36"/>
-      <c r="G46" s="36"/>
-      <c r="H46" s="36"/>
-      <c r="I46" s="36"/>
+      <c r="A46" s="37"/>
+      <c r="B46" s="37"/>
+      <c r="C46" s="37"/>
+      <c r="D46" s="37"/>
+      <c r="E46" s="37"/>
+      <c r="F46" s="37"/>
+      <c r="G46" s="37"/>
+      <c r="H46" s="37"/>
+      <c r="I46" s="37"/>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A47" s="36"/>
-      <c r="B47" s="36"/>
-      <c r="C47" s="36"/>
-      <c r="D47" s="36"/>
-      <c r="E47" s="36"/>
-      <c r="F47" s="36"/>
-      <c r="G47" s="36"/>
-      <c r="H47" s="36"/>
-      <c r="I47" s="36"/>
+      <c r="A47" s="37"/>
+      <c r="B47" s="37"/>
+      <c r="C47" s="37"/>
+      <c r="D47" s="37"/>
+      <c r="E47" s="37"/>
+      <c r="F47" s="37"/>
+      <c r="G47" s="37"/>
+      <c r="H47" s="37"/>
+      <c r="I47" s="37"/>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A48" s="36"/>
-      <c r="B48" s="36"/>
-      <c r="C48" s="36"/>
-      <c r="D48" s="36"/>
-      <c r="E48" s="36"/>
-      <c r="F48" s="36"/>
-      <c r="G48" s="36"/>
-      <c r="H48" s="36"/>
-      <c r="I48" s="36"/>
+      <c r="A48" s="37"/>
+      <c r="B48" s="37"/>
+      <c r="C48" s="37"/>
+      <c r="D48" s="37"/>
+      <c r="E48" s="37"/>
+      <c r="F48" s="37"/>
+      <c r="G48" s="37"/>
+      <c r="H48" s="37"/>
+      <c r="I48" s="37"/>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A49" s="36"/>
-      <c r="B49" s="36"/>
-      <c r="C49" s="36"/>
-      <c r="D49" s="36"/>
-      <c r="E49" s="36"/>
-      <c r="F49" s="36"/>
-      <c r="G49" s="36"/>
-      <c r="H49" s="36"/>
-      <c r="I49" s="36"/>
+      <c r="A49" s="37"/>
+      <c r="B49" s="37"/>
+      <c r="C49" s="37"/>
+      <c r="D49" s="37"/>
+      <c r="E49" s="37"/>
+      <c r="F49" s="37"/>
+      <c r="G49" s="37"/>
+      <c r="H49" s="37"/>
+      <c r="I49" s="37"/>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A50" s="36"/>
-      <c r="B50" s="36"/>
-      <c r="C50" s="36"/>
-      <c r="D50" s="36"/>
-      <c r="E50" s="36"/>
-      <c r="F50" s="36"/>
-      <c r="G50" s="36"/>
-      <c r="H50" s="36"/>
-      <c r="I50" s="36"/>
+      <c r="A50" s="37"/>
+      <c r="B50" s="37"/>
+      <c r="C50" s="37"/>
+      <c r="D50" s="37"/>
+      <c r="E50" s="37"/>
+      <c r="F50" s="37"/>
+      <c r="G50" s="37"/>
+      <c r="H50" s="37"/>
+      <c r="I50" s="37"/>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A51" s="36"/>
-      <c r="B51" s="36"/>
-      <c r="C51" s="36"/>
-      <c r="D51" s="36"/>
-      <c r="E51" s="36"/>
-      <c r="F51" s="36"/>
-      <c r="G51" s="36"/>
-      <c r="H51" s="36"/>
-      <c r="I51" s="36"/>
+      <c r="A51" s="37"/>
+      <c r="B51" s="37"/>
+      <c r="C51" s="37"/>
+      <c r="D51" s="37"/>
+      <c r="E51" s="37"/>
+      <c r="F51" s="37"/>
+      <c r="G51" s="37"/>
+      <c r="H51" s="37"/>
+      <c r="I51" s="37"/>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A52" s="36"/>
-      <c r="B52" s="36"/>
-      <c r="C52" s="36"/>
-      <c r="D52" s="36"/>
-      <c r="E52" s="36"/>
-      <c r="F52" s="36"/>
-      <c r="G52" s="36"/>
-      <c r="H52" s="36"/>
-      <c r="I52" s="36"/>
+      <c r="A52" s="37"/>
+      <c r="B52" s="37"/>
+      <c r="C52" s="37"/>
+      <c r="D52" s="37"/>
+      <c r="E52" s="37"/>
+      <c r="F52" s="37"/>
+      <c r="G52" s="37"/>
+      <c r="H52" s="37"/>
+      <c r="I52" s="37"/>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A53" s="36"/>
-      <c r="B53" s="37"/>
+      <c r="A53" s="37"/>
+      <c r="B53" s="42"/>
       <c r="C53" s="33"/>
       <c r="D53" s="33"/>
       <c r="E53" s="33"/>
       <c r="F53" s="34"/>
       <c r="G53" s="34"/>
-      <c r="H53" s="38"/>
+      <c r="H53" s="43"/>
       <c r="I53" s="35"/>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A54" s="39" t="s">
+      <c r="A54" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="B54" s="39"/>
-      <c r="C54" s="40" t="s">
+      <c r="B54" s="44"/>
+      <c r="C54" s="45" t="s">
         <v>44</v>
       </c>
-      <c r="D54" s="41"/>
-      <c r="E54" s="41"/>
-      <c r="F54" s="41"/>
-      <c r="G54" s="41"/>
-      <c r="H54" s="42"/>
-      <c r="I54" s="43">
-        <v>32.21</v>
+      <c r="D54" s="46"/>
+      <c r="E54" s="46"/>
+      <c r="F54" s="46"/>
+      <c r="G54" s="46"/>
+      <c r="H54" s="47"/>
+      <c r="I54" s="48">
+        <v>30.08</v>
       </c>
     </row>
     <row r="55" ht="90.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A55" s="44"/>
-      <c r="B55" s="45"/>
-      <c r="C55" s="45"/>
-      <c r="D55" s="45"/>
-      <c r="E55" s="45"/>
-      <c r="F55" s="45"/>
-      <c r="G55" s="45"/>
-      <c r="H55" s="45"/>
-      <c r="I55" s="46"/>
+      <c r="A55" s="49"/>
+      <c r="B55" s="50"/>
+      <c r="C55" s="50"/>
+      <c r="D55" s="50"/>
+      <c r="E55" s="50"/>
+      <c r="F55" s="50"/>
+      <c r="G55" s="50"/>
+      <c r="H55" s="50"/>
+      <c r="I55" s="51"/>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A56" s="47"/>
-      <c r="B56" s="48"/>
-      <c r="C56" s="48"/>
-      <c r="D56" s="48"/>
-      <c r="E56" s="48"/>
-      <c r="F56" s="48"/>
-      <c r="G56" s="48"/>
-      <c r="H56" s="48"/>
-      <c r="I56" s="49"/>
+      <c r="A56" s="52"/>
+      <c r="B56" s="53"/>
+      <c r="C56" s="53"/>
+      <c r="D56" s="53"/>
+      <c r="E56" s="53"/>
+      <c r="F56" s="53"/>
+      <c r="G56" s="53"/>
+      <c r="H56" s="53"/>
+      <c r="I56" s="54"/>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A57" s="47"/>
-      <c r="B57" s="48"/>
-      <c r="C57" s="48"/>
-      <c r="D57" s="48"/>
-      <c r="E57" s="48"/>
-      <c r="F57" s="48"/>
-      <c r="G57" s="48"/>
-      <c r="H57" s="48"/>
-      <c r="I57" s="49"/>
+      <c r="A57" s="52"/>
+      <c r="B57" s="53"/>
+      <c r="C57" s="53"/>
+      <c r="D57" s="53"/>
+      <c r="E57" s="53"/>
+      <c r="F57" s="53"/>
+      <c r="G57" s="53"/>
+      <c r="H57" s="53"/>
+      <c r="I57" s="54"/>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A58" s="47"/>
-      <c r="B58" s="48"/>
-      <c r="C58" s="48"/>
-      <c r="D58" s="48"/>
-      <c r="E58" s="48"/>
-      <c r="F58" s="48"/>
-      <c r="G58" s="48"/>
-      <c r="H58" s="48"/>
-      <c r="I58" s="49"/>
+      <c r="A58" s="52"/>
+      <c r="B58" s="53"/>
+      <c r="C58" s="53"/>
+      <c r="D58" s="53"/>
+      <c r="E58" s="53"/>
+      <c r="F58" s="53"/>
+      <c r="G58" s="53"/>
+      <c r="H58" s="53"/>
+      <c r="I58" s="54"/>
     </row>
     <row r="59" ht="85.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A59" s="47"/>
-      <c r="B59" s="48"/>
-      <c r="C59" s="48"/>
-      <c r="D59" s="48"/>
-      <c r="E59" s="48"/>
-      <c r="F59" s="48"/>
-      <c r="G59" s="48"/>
-      <c r="H59" s="48"/>
-      <c r="I59" s="49"/>
+      <c r="A59" s="52"/>
+      <c r="B59" s="53"/>
+      <c r="C59" s="53"/>
+      <c r="D59" s="53"/>
+      <c r="E59" s="53"/>
+      <c r="F59" s="53"/>
+      <c r="G59" s="53"/>
+      <c r="H59" s="53"/>
+      <c r="I59" s="54"/>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A60" s="47"/>
-      <c r="B60" s="50" t="s">
+      <c r="A60" s="52"/>
+      <c r="B60" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="C60" s="51" t="s">
+      <c r="C60" s="56" t="s">
         <v>46</v>
       </c>
-      <c r="D60" s="52"/>
-      <c r="E60" s="53"/>
-      <c r="F60" s="53"/>
-      <c r="G60" s="53"/>
-      <c r="H60" s="53"/>
-      <c r="I60" s="54"/>
+      <c r="D60" s="57"/>
+      <c r="E60" s="58"/>
+      <c r="F60" s="58"/>
+      <c r="G60" s="58"/>
+      <c r="H60" s="58"/>
+      <c r="I60" s="59"/>
     </row>
     <row r="61" ht="25.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A61" s="47"/>
-      <c r="B61" s="55" t="s">
+      <c r="A61" s="52"/>
+      <c r="B61" s="60" t="s">
         <v>47</v>
       </c>
-      <c r="C61" s="56" t="s">
-        <v>11</v>
-      </c>
-      <c r="D61" s="53"/>
-      <c r="E61" s="53"/>
-      <c r="F61" s="53"/>
-      <c r="G61" s="53"/>
-      <c r="H61" s="53"/>
-      <c r="I61" s="54"/>
+      <c r="C61" s="61" t="s">
+        <v>48</v>
+      </c>
+      <c r="D61" s="58"/>
+      <c r="E61" s="58"/>
+      <c r="F61" s="58"/>
+      <c r="G61" s="58"/>
+      <c r="H61" s="58"/>
+      <c r="I61" s="59"/>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A62" s="47"/>
-      <c r="B62" s="57" t="s">
-        <v>48</v>
-      </c>
-      <c r="C62" s="58" t="s">
+      <c r="A62" s="52"/>
+      <c r="B62" s="62" t="s">
         <v>49</v>
       </c>
-      <c r="D62" s="53"/>
-      <c r="E62" s="53"/>
-      <c r="F62" s="53"/>
-      <c r="G62" s="59"/>
-      <c r="H62" s="60"/>
-      <c r="I62" s="61"/>
+      <c r="C62" s="63" t="s">
+        <v>50</v>
+      </c>
+      <c r="D62" s="58"/>
+      <c r="E62" s="58"/>
+      <c r="F62" s="58"/>
+      <c r="G62" s="64"/>
+      <c r="H62" s="65"/>
+      <c r="I62" s="66"/>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A63" s="47"/>
-      <c r="B63" s="53"/>
-      <c r="C63" s="53"/>
-      <c r="D63" s="53"/>
-      <c r="E63" s="53"/>
-      <c r="F63" s="53"/>
-      <c r="G63" s="53"/>
-      <c r="H63" s="53"/>
-      <c r="I63" s="61"/>
+      <c r="A63" s="52"/>
+      <c r="B63" s="58"/>
+      <c r="C63" s="58"/>
+      <c r="D63" s="58"/>
+      <c r="E63" s="58"/>
+      <c r="F63" s="58"/>
+      <c r="G63" s="58"/>
+      <c r="H63" s="58"/>
+      <c r="I63" s="66"/>
     </row>
     <row r="64" ht="72.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A64" s="47"/>
-      <c r="B64" s="53"/>
-      <c r="C64" s="53"/>
-      <c r="D64" s="53"/>
-      <c r="E64" s="53"/>
-      <c r="F64" s="53"/>
-      <c r="G64" s="53"/>
-      <c r="H64" s="53"/>
-      <c r="I64" s="54"/>
+      <c r="A64" s="52"/>
+      <c r="B64" s="58"/>
+      <c r="C64" s="58"/>
+      <c r="D64" s="58"/>
+      <c r="E64" s="58"/>
+      <c r="F64" s="58"/>
+      <c r="G64" s="58"/>
+      <c r="H64" s="58"/>
+      <c r="I64" s="59"/>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A65" s="47"/>
-      <c r="B65" s="50" t="s">
+      <c r="A65" s="52"/>
+      <c r="B65" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="C65" s="51" t="s">
-        <v>50</v>
-      </c>
-      <c r="D65" s="53"/>
-      <c r="E65" s="53"/>
-      <c r="F65" s="53"/>
-      <c r="G65" s="53"/>
-      <c r="H65" s="53"/>
-      <c r="I65" s="54"/>
+      <c r="C65" s="56" t="s">
+        <v>51</v>
+      </c>
+      <c r="D65" s="58"/>
+      <c r="E65" s="58"/>
+      <c r="F65" s="58"/>
+      <c r="G65" s="58"/>
+      <c r="H65" s="58"/>
+      <c r="I65" s="59"/>
     </row>
     <row r="66" ht="25.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A66" s="47"/>
-      <c r="B66" s="55" t="s">
+      <c r="A66" s="52"/>
+      <c r="B66" s="60" t="s">
         <v>47</v>
       </c>
-      <c r="C66" s="56" t="s">
-        <v>11</v>
-      </c>
-      <c r="D66" s="53"/>
-      <c r="E66" s="53"/>
-      <c r="F66" s="53"/>
-      <c r="G66" s="53"/>
-      <c r="H66" s="53"/>
-      <c r="I66" s="54"/>
+      <c r="C66" s="61" t="s">
+        <v>52</v>
+      </c>
+      <c r="D66" s="58"/>
+      <c r="E66" s="58"/>
+      <c r="F66" s="58"/>
+      <c r="G66" s="58"/>
+      <c r="H66" s="58"/>
+      <c r="I66" s="59"/>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A67" s="47"/>
-      <c r="B67" s="57" t="s">
-        <v>48</v>
-      </c>
-      <c r="C67" s="58" t="s">
-        <v>51</v>
-      </c>
-      <c r="D67" s="53"/>
-      <c r="E67" s="53"/>
-      <c r="F67" s="53"/>
-      <c r="G67" s="59"/>
-      <c r="H67" s="60"/>
-      <c r="I67" s="54"/>
+      <c r="A67" s="52"/>
+      <c r="B67" s="62" t="s">
+        <v>49</v>
+      </c>
+      <c r="C67" s="63" t="s">
+        <v>53</v>
+      </c>
+      <c r="D67" s="58"/>
+      <c r="E67" s="58"/>
+      <c r="F67" s="58"/>
+      <c r="G67" s="64"/>
+      <c r="H67" s="65"/>
+      <c r="I67" s="59"/>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A68" s="62"/>
-      <c r="B68" s="60"/>
-      <c r="C68" s="60"/>
-      <c r="D68" s="60"/>
-      <c r="E68" s="60"/>
-      <c r="F68" s="60"/>
-      <c r="G68" s="60"/>
-      <c r="H68" s="60"/>
-      <c r="I68" s="63"/>
+      <c r="A68" s="67"/>
+      <c r="B68" s="65"/>
+      <c r="C68" s="65"/>
+      <c r="D68" s="65"/>
+      <c r="E68" s="65"/>
+      <c r="F68" s="65"/>
+      <c r="G68" s="65"/>
+      <c r="H68" s="65"/>
+      <c r="I68" s="68"/>
     </row>
   </sheetData>
   <mergeCells count="6">
